--- a/naver-place-crawler/results_health/의정부_PT.xlsx
+++ b/naver-place-crawler/results_health/의정부_PT.xlsx
@@ -417,16 +417,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="39" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -559,39 +559,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>다이어트,비만</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>메이드라인 다이어트 의정부점</t>
+          <t>체육시간</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>madeline-@naver.com</t>
+          <t>time6943@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1304-3854</t>
+          <t>0507-1416-8281</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 의정부시 가능로 105 성원빌딩 4층</t>
+          <t>경기도 의정부시 오목로205번길 61 5층 체육시간</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://made-line.co.kr</t>
+          <t>https://www.instagram.com/pttime_gym</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -601,19 +601,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4poji</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>667</v>
+        <v>65</v>
       </c>
       <c r="Q2" t="n">
-        <v>285</v>
+        <v>331</v>
       </c>
       <c r="R2" t="n">
-        <v>952</v>
+        <v>396</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,56 +636,56 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1572526028</t>
+          <t>931357548</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1572526028</t>
+          <t>https://m.place.naver.com/place/931357548</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>바디챌린지트레이닝센터</t>
+          <t>와이바디짐</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>tkatozl@naver.com</t>
+          <t>whdudwls16@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1401-2199</t>
+          <t>0507-1314-4517</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 의정부시 오목로205번길 1 예스타워 7층 702호</t>
+          <t>경기도 의정부시 용민로 473 폴리프라자I 3층 와이바디짐(영바디짐)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/</t>
+          <t>https://blog.naver.com/whdudwls16</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -699,19 +695,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcs46b</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -719,17 +711,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>70</v>
+        <v>147</v>
       </c>
       <c r="Q3" t="n">
-        <v>252</v>
+        <v>185</v>
       </c>
       <c r="R3" t="n">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,51 +730,51 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>37775706</t>
+          <t>1300750769</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37775706</t>
+          <t>https://m.place.naver.com/place/1300750769</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>휴먼 근골격 운동센터 의정부 PT 민락점</t>
+          <t>지엘핏 헬스 &amp; PT 가능점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>hue_musculoskeleta@naver.com</t>
+          <t>zielfit2@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1456-0358</t>
+          <t>0507-1406-9244</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 의정부시 오목로205번길 21 골든프라자3차 4층 404-1호</t>
+          <t>경기도 의정부시 신촌로29번길 24 3층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hue_musculoskeleta</t>
+          <t>https://blog.naver.com/zielfit2</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -802,14 +794,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4h5hq</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -821,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>358</v>
+        <v>549</v>
       </c>
       <c r="Q4" t="n">
-        <v>1490</v>
+        <v>355</v>
       </c>
       <c r="R4" t="n">
-        <v>1848</v>
+        <v>904</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1045318033</t>
+          <t>1335830135</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1045318033</t>
+          <t>https://m.place.naver.com/place/1335830135</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -858,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>바디붐휘트니스 민락점 헬스&amp;PT</t>
+          <t>핏사이클</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>bodyboom_pt@naver.com</t>
+          <t>hnb_9293@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>031-851-3456</t>
+          <t>031-877-0815</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 의정부시 오목로225번길 140 성산타워7층</t>
+          <t>경기도 의정부시 평화로190번길 9 2층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/piece_gym_031_480_6565</t>
+          <t>http://instagram.com/fitcycle.kr</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -915,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1160</v>
+        <v>115</v>
       </c>
       <c r="Q5" t="n">
-        <v>732</v>
+        <v>47</v>
       </c>
       <c r="R5" t="n">
-        <v>1892</v>
+        <v>162</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>36680429</t>
+          <t>1179826542</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36680429</t>
+          <t>https://m.place.naver.com/place/1179826542</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -952,29 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>웨이포 트레이닝센터 PT</t>
+          <t>마인딩 PT 망월사점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>jerry_training@naver.com</t>
+          <t>wonkyu0921@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1429-1009</t>
+          <t>0507-1374-5431</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 의정부시 시민로 27 지층 01,02호 남해오네뜨</t>
+          <t>경기도 의정부시 호암로 141 4층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/way_four_pt</t>
+          <t>https://blog.naver.com/wonkyu0921</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -989,19 +977,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5wzaw</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1013,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>119</v>
+        <v>28</v>
       </c>
       <c r="Q6" t="n">
-        <v>198</v>
+        <v>7</v>
       </c>
       <c r="R6" t="n">
-        <v>317</v>
+        <v>35</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1263561165</t>
+          <t>1085744237</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1263561165</t>
+          <t>https://m.place.naver.com/place/1085744237</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1050,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>스포애니 의정부역점</t>
+          <t>굿모닝휘트니스</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>spoany_62@naver.com</t>
+          <t>pinelemon@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1409-9618</t>
+          <t>0507-1389-7377</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 의정부시 평화로 540 9, 10 층</t>
+          <t>경기도 의정부시 동일로 583 롯데슈퍼 2층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spoany_62</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1082,24 +1066,20 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4fckh</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1107,17 +1087,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2016</v>
+        <v>4</v>
       </c>
       <c r="Q7" t="n">
-        <v>1950</v>
+        <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>3966</v>
+        <v>10</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,51 +1106,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1886274354</t>
+          <t>11597212</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1886274354</t>
+          <t>https://m.place.naver.com/place/11597212</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>아테나휘트니스</t>
+          <t>코어짐 망월사역점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>athenagym@naver.com</t>
+          <t>coregym0045@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1334-7642</t>
+          <t>0507-1493-1198</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 의정부시 시민로121번길 28 지하1층</t>
+          <t>경기도 의정부시 평화로 180 진양빌딩 5층 코어짐</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/athenagym</t>
+          <t>https://www.instagram.com/coregym_0045/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1185,19 +1165,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5z8kw</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1209,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2898</v>
+        <v>23</v>
       </c>
       <c r="Q8" t="n">
-        <v>964</v>
+        <v>34</v>
       </c>
       <c r="R8" t="n">
-        <v>3862</v>
+        <v>57</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,47 +1200,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1788806049</t>
+          <t>1066465475</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1788806049</t>
+          <t>https://m.place.naver.com/place/1066465475</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>한번더재활운동센터</t>
+          <t>아테나휘트니스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>kongja21@naver.com</t>
+          <t>athenagym@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0507-1334-7642</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 의정부시 세석로 20 2층 204호</t>
+          <t>경기도 의정부시 시민로121번길 28 지하1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://youtube.com/@한번더재활운동센터</t>
+          <t>https://blog.naver.com/athenagym</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1279,19 +1259,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/weppdix</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1299,17 +1275,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>58</v>
+        <v>2910</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>967</v>
       </c>
       <c r="R9" t="n">
-        <v>60</v>
+        <v>3877</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,51 +1294,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2072368822</t>
+          <t>1788806049</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2072368822</t>
+          <t>https://m.place.naver.com/place/1788806049</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>요가원</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>의정부요가&amp;필라테스 힐피요</t>
+          <t>리츠피트니스</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>yogapilates1@naver.com</t>
+          <t>1991xbox@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1461-1391</t>
+          <t>0507-1390-6091</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 의정부시 시민로 125 8층</t>
+          <t>경기도 의정부시 청사로47번길 12 성산타워 2층 203호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/yogapilates1</t>
+          <t>https://www.instagram.com/rits_fitness2024</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1377,19 +1353,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4shlq</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1401,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="Q10" t="n">
-        <v>172</v>
+        <v>28</v>
       </c>
       <c r="R10" t="n">
-        <v>249</v>
+        <v>85</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,56 +1388,56 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1284766203</t>
+          <t>1335529463</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1284766203</t>
+          <t>https://m.place.naver.com/place/1335529463</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>코스트짐PT 민락점</t>
+          <t>피트니스플레이스 헬스&amp;PT 장암점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>costgymjun@naver.com</t>
+          <t>fitnessplace5@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>031-853-1663</t>
+          <t>0507-1414-9679</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 의정부시 오목로205번길 21 골든프라자 3차 202호</t>
+          <t>경기도 의정부시 회룡로 188 장암골드프라자 지하2층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/costgym</t>
+          <t>https://pf.kakao.com/_xmxkhTG</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1486,7 +1458,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1495,13 +1467,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>90</v>
+        <v>736</v>
       </c>
       <c r="Q11" t="n">
-        <v>84</v>
+        <v>192</v>
       </c>
       <c r="R11" t="n">
-        <v>174</v>
+        <v>928</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1510,51 +1482,51 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>38447811</t>
+          <t>1658324530</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38447811</t>
+          <t>https://m.place.naver.com/place/1658324530</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>필라테스 림 탑석역 점</t>
+          <t>원앤원짐 민락점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>pilateslim201@naver.com</t>
+          <t>oneonegym@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1440-2832</t>
+          <t>0507-1420-1262</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기 의정부시 오목로 33 2층 201호</t>
+          <t>경기도 의정부시 용현로105번길 33-1 5층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/pilateslim201/224181377037</t>
+          <t>https://blog.naver.com/oneonegym</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1574,14 +1546,10 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wjnmgc7</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>O</t>
@@ -1593,13 +1561,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>706</v>
+        <v>112</v>
       </c>
       <c r="Q12" t="n">
-        <v>1059</v>
+        <v>376</v>
       </c>
       <c r="R12" t="n">
-        <v>1765</v>
+        <v>488</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1608,17 +1576,7299 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1347002622</t>
+          <t>1562499899</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1347002622</t>
+          <t>https://m.place.naver.com/place/1562499899</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>휴먼 근골격 운동센터 의정부 PT 민락점</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>hue_musculoskeleta@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1456-0358</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 오목로205번길 21 골든프라자3차 4층 404-1호</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/hue_musculoskeleta</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>358</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1495</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1853</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1045318033</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1045318033</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>코어짐</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>coregym0045@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1494-0045</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 외미로 104-12 유타상가 6층 코어짐</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/coregym0045</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>71</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>147</v>
+      </c>
+      <c r="R14" t="n">
+        <v>218</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1941497073</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1941497073</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>포레스포 헬스PT 골프 필라테스 클라이밍</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>incar50@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0507-1365-6211</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 청사로47번길 18 로얄프라자 6층 601~603호</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/incar50</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>575</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>276</v>
+      </c>
+      <c r="R15" t="n">
+        <v>851</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1258663714</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1258663714</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>부티크짐 퍼스널 헬스&amp;PT 라운지</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>junibu11@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0507-1352-9402</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 신흥로 136 3층 301호</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_xiZhBG</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>47</v>
+      </c>
+      <c r="R16" t="n">
+        <v>121</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1183124719</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1183124719</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>맥스짐</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>bestkr2002@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0507-1342-4601</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 평화로 186-1 3층</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bestkr2002</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>23</v>
+      </c>
+      <c r="R17" t="n">
+        <v>26</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1326835740</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1326835740</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>핏밀리 의정부점</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>fit_mily@naver.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 동일로747번길 57 외 11번지 을지타워 3층 309호</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/fitmilystore</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>9</v>
+      </c>
+      <c r="R18" t="n">
+        <v>10</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1703364047</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1703364047</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>여성전용 하이핏 의정부PT</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>highfit1@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0507-1383-2285</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 신흥로 193 동일빌딩 6층</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/highfit01</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>511</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>542</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1053</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>1119319383</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1119319383</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>얼라이브짐</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>rbtjd2411@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0507-1356-9171</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 장곡로628번길 22 삼성플러스 1201호</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/rbtjd2411</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>131</v>
+      </c>
+      <c r="R20" t="n">
+        <v>167</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1405998650</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1405998650</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>허준PT</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>joon0728@naver.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0507-1399-5572</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 장곡로 554 501호</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/with_jun86/</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>7</v>
+      </c>
+      <c r="R21" t="n">
+        <v>23</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1454800606</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1454800606</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>인생퍼스널트레이닝PT</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>nb0697@naver.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0507-1340-4117</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 동일로 456 5층</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/nb0697</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>211</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>188</v>
+      </c>
+      <c r="R22" t="n">
+        <v>399</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>1156319685</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1156319685</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>꿀핏휘트니스 신곡점</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>honeyfit_3@naver.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0507-1434-2439</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 추동로 15 대명프라자 6층</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=Xw10EOdN3w8</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>142</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>630</v>
+      </c>
+      <c r="R23" t="n">
+        <v>772</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>2070790169</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2070790169</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>올바른 PT &amp; 헬스</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>allbarun_pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0507-1491-1237</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 시민로 81 서부타워빌딩 8층 804호</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/allbarun_pt</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>98</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>148</v>
+      </c>
+      <c r="R24" t="n">
+        <v>246</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>1486375887</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1486375887</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>희핏 PT&amp;헬스</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>heegym@naver.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0507-1459-0281</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 평화로 432 지하1층</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/heegym</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>188</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>455</v>
+      </c>
+      <c r="R25" t="n">
+        <v>643</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>1135733595</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1135733595</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>제이든퍼스널트레이닝 PT&amp;헬스 의정부점</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>jayden_pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0507-1351-2449</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 시민로 39 403호</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_xlxbxcHxj</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>219</v>
+      </c>
+      <c r="R26" t="n">
+        <v>296</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>1585345364</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1585345364</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>가능해짐 헬스&amp;PT 2호점</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>9939205@naver.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0507-1399-3129</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 신흥로 357 2층</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/9939205</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>84</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>233</v>
+      </c>
+      <c r="R27" t="n">
+        <v>317</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1569013795</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1569013795</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>김현제pt</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>wjdtnswn006@naver.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0507-1393-3858</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 오목로225번길 105 뉴욕뉴욕 프라자 5층</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hyun_je_pt/</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>153</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>220</v>
+      </c>
+      <c r="R28" t="n">
+        <v>373</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1734637665</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1734637665</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>바디ON 여성전용PT 탑석역 용현점</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>moclab@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0507-1358-8954</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 용민로 10 탑석센트럴자이 아파트, 정문상가 2층</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/body_ongym</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>5</v>
+      </c>
+      <c r="R29" t="n">
+        <v>44</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>1717983937</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1717983937</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>바디붐휘트니스 민락점 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>bodyboom_pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>031-851-3456</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 오목로225번길 140 성산타워7층</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/piece_gym_031_480_6565</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>1166</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>734</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1900</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>36680429</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36680429</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>리, 숨 웰니스 클럽</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>resum_wellness@naver.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0507-1311-4842</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 용민로 22 3층 리숨 웰니스클럽</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_hxhixbn</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>41</v>
+      </c>
+      <c r="R31" t="n">
+        <v>79</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>1351882582</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1351882582</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>얼리버드짐 2호점</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>earlybirdgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0507-1471-4451</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 시민로 237 5층</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/earlybirdgym</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>95</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>40</v>
+      </c>
+      <c r="R32" t="n">
+        <v>135</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>2003715056</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2003715056</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>도이연 피트니스 라운지</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>doiyeonfitnesslounge@naver.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0507-1426-5088</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 오목로 227 5층 501호</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/doiyeon_fitnesslounge</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>6</v>
+      </c>
+      <c r="R33" t="n">
+        <v>30</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>1026428945</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1026428945</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>리핏트레이닝센터 의정부 PT 민락점</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>sun1257you@naver.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0507-1381-5644</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 용현로105번길 23 메디컬빌딩 8층</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>http://instagram.com/leefit_training</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>318</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>524</v>
+      </c>
+      <c r="R34" t="n">
+        <v>842</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>1796288373</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1796288373</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>리얼타임피트니스 용현점</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>realtimefitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0507-1328-9679</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 충의로57번길 18 2층</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/realtimefitness</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>93</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>22</v>
+      </c>
+      <c r="R35" t="n">
+        <v>115</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>1893694712</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1893694712</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>삼성휘트니스</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>samsung_fit@naver.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>031-836-9772</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 신곡로 47 우신프라자 5층</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/samsung_fitness_/</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>106</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>477</v>
+      </c>
+      <c r="R36" t="n">
+        <v>583</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>19578878</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/19578878</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>픽짐PT 의정부 민락점</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>picgym_pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0507-1387-2032</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 오목로205번길 29 골든프라자2차 4층 픽짐</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://youtube.com/@picgym</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>121</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>199</v>
+      </c>
+      <c r="R37" t="n">
+        <v>320</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>1570416248</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1570416248</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>여성전용 원바디짐</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>onebodygym@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0507-1316-8722</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 평화로 195</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/onebodygym</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>120</v>
+      </c>
+      <c r="R38" t="n">
+        <v>142</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>1890695063</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1890695063</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>코스트짐PT 민락점</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>costgymjun@naver.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>031-853-1663</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 오목로205번길 21 골든프라자 3차 202호</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/costgym</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>84</v>
+      </c>
+      <c r="R39" t="n">
+        <v>174</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>38447811</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38447811</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>치유짐24 헬스 PT 민락점</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>cldbgym3@naver.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0507-1344-4446</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 효자로 14 801호, 802호</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/cldbgym3</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>22</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>2009439517</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2009439517</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>위어짐PT스튜디오</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>weagym@naver.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0507-1353-6358</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 평화로 147 2층</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/weagym_official?igsh=MWhvYWdrcXh1Z2w3aw%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>87</v>
+      </c>
+      <c r="R41" t="n">
+        <v>126</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1237647202</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1237647202</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>여성전용 핏걸 PT &amp; 필라테스</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>fitgirl6@naver.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>031-821-2262</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 평화로 628 6층 핏걸가능점</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/fitgirl6</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>212</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>328</v>
+      </c>
+      <c r="R42" t="n">
+        <v>540</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1598338046</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1598338046</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>얼리버드짐</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>earlybirdgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0507-1301-1421</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 발곡로 22 신풍프라자 B1층 전체</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/earlybirdgym</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>1564</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>916</v>
+      </c>
+      <c r="R43" t="n">
+        <v>2480</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1921522541</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1921522541</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>초이PT</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>choiptstudioo@naver.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0507-1372-7674</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 월유로 16 GS프라자 6층 초이PT스튜디오</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://open.kakao.com/o/sOUBRHVd</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>74</v>
+      </c>
+      <c r="R44" t="n">
+        <v>154</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1312778248</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1312778248</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>오메가짐 헬스&amp;PT 민락점</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ounha_gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1472-3611</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 용민로 192 7층</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ounha_gym</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>3</v>
+      </c>
+      <c r="R45" t="n">
+        <v>5</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>2028181993</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2028181993</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>올인짐 의정부본점</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>brakofficial@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0507-1397-4344</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 충의로 25 5층 501~508호</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/allin_gym1?igsh=Yzk1bGZicTR1dmEw&amp;utm_source=qr/</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>779</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>245</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1024</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>2023029424</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2023029424</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>안녕PT 스튜디오</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>annyeongpt@naver.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1384-5041</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 월유로 13 504호, 안녕피티</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/annyeongpt</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>58</v>
+      </c>
+      <c r="R47" t="n">
+        <v>94</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>1350369204</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1350369204</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>레이디핏 여성전용 PT 헬스</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>slimfit12@naver.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>031-847-1318</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 호국로 1318 우체국 2층</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/slimfit12</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>390</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>584</v>
+      </c>
+      <c r="R48" t="n">
+        <v>974</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>1053007238</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1053007238</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>탑클래스 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>guswnsdla182@naver.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>031-836-1114</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 회룡로 141 다운빌딩 3층 탑클래스휘트니스</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/guswnsdla182</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>218</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>131</v>
+      </c>
+      <c r="R49" t="n">
+        <v>349</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>1201949015</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1201949015</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>바디조아짐PT</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1sudong4341@naver.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0507-1324-7031</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 오목로 23 2층 바디조아짐</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/1sudong4341</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>125</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>99</v>
+      </c>
+      <c r="R50" t="n">
+        <v>224</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>1300846978</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1300846978</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>SM BUM 휘트니스</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>smbum1@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0507-1485-2220</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 오목로 233 예지플러스 3층</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/smbum1</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>165</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>64</v>
+      </c>
+      <c r="R51" t="n">
+        <v>229</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>1503441721</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1503441721</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>데이짐휘트니스 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>daygym_@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0507-1410-7247</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 평화로 271-9 상가동 지층 101호</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/daygym_01</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>106</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>85</v>
+      </c>
+      <c r="R52" t="n">
+        <v>191</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>2090105529</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2090105529</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>여성전용PT 퀸메이커짐 의정부점</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>loveis1274@naver.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>ndltkdxor1274@gmail.com</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0507-1313-3274</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 범골로 94 3층 301호</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@tvsangtaek7235</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>114</v>
+      </c>
+      <c r="R53" t="n">
+        <v>152</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1413273266</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1413273266</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>의정부짐</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>dmlwjdqnwla1@naver.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1386-8583</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 경의로 108 한양수자인파크뷰 B101호</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/dmlwjdqnwla1</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>1014</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>670</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1684</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1267068271</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1267068271</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>유투핏PT</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>u2fitpt_uijeongbu@naver.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0507-1448-9682</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 오목로18번길 2 3층</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/u2fitpt_uijeongbu</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>194</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>283</v>
+      </c>
+      <c r="R55" t="n">
+        <v>477</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>1536642285</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1536642285</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>번지피지오 바나다번지앤핏</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2020banada@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0507-1379-1929</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 청사로 41 7층 705호</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://https//open.kakao.com/me/2020banada</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>189</v>
+      </c>
+      <c r="R56" t="n">
+        <v>197</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>1003021739</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1003021739</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>브랜뉴핏 헬스&amp;PT 낙양점</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>guddls2030@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0507-1324-9688</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 민락로 398 대훈프라자3층 브랜뉴핏</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://youtube.com/@Mr.kinglion</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>1961</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>66</v>
+      </c>
+      <c r="R57" t="n">
+        <v>2027</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>1765268638</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1765268638</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>NEWGYM뉴짐 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>newgym_@naver.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0507-1353-4558</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 태평로 18-2 아이콘스타 3차 B1</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@village1533</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>27</v>
+      </c>
+      <c r="R58" t="n">
+        <v>45</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>1978167226</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1978167226</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>테크니티 스포츠과학 AI 운동센터</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>bs5819@naver.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0507-1336-5819</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 둔야로 12 2층 202호</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bs5819/223888868265</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>20</v>
+      </c>
+      <c r="R59" t="n">
+        <v>20</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>2002089286</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2002089286</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>프로짐 헬스&amp;PT 고산점</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>progym01@naver.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0507-1470-1675</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 서광로 205 유성빌딩 4F 프로짐 피트니스</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=2u4sR28Hdis</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>34</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>40</v>
+      </c>
+      <c r="R60" t="n">
+        <v>74</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>2064727181</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2064727181</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>쿠키짐</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>gymck@naver.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0507-1390-4997</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 발곡로 24 303, 304호</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/gymck</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>16</v>
+      </c>
+      <c r="R61" t="n">
+        <v>41</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>1096663145</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1096663145</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>디디짐</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>d_dgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0507-1349-2054</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 의정로 84 지하1층</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://shard-fountain-a04.notion.site/d_d-GYM-2ef16ac9b6d98012b472f8a9028136a9?source=copy_link</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>37</v>
+      </c>
+      <c r="R62" t="n">
+        <v>100</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>1925795514</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1925795514</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>마인딩 PT 민락점</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>wonkyu0921@naver.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0507-1466-5431</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 용현로105번길 19 3층</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/wonkyu0921</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>95</v>
+      </c>
+      <c r="R63" t="n">
+        <v>158</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>1111179493</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1111179493</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>브랜뉴핏 헬스&amp;PT 민락점</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>guddls2030@naver.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>koreaart@koreaart.ac.kr</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0507-1340-8304</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 오목로225번길 95 도영빌딩 2층</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://www.koreaart.ac.kr/faculty/sports/pfsView.asp?idx=2445</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>1032</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>114</v>
+      </c>
+      <c r="R64" t="n">
+        <v>1146</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>1214321010</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1214321010</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>바디랩스</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>hogn1010@naver.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0507-1369-4460</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 부용로 95 202호 바디랩스</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/hogn1010</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>46</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>9</v>
+      </c>
+      <c r="R65" t="n">
+        <v>55</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>1260971947</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1260971947</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>원앤원짐 의정부역점</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>oneone8080@naver.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0507-1464-1630</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 평화로542번길 13</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/oneone8080</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>287</v>
+      </c>
+      <c r="R66" t="n">
+        <v>344</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>1501235333</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1501235333</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>글로벌 운동재활센터 녹양점</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>ehdtjs7830@naver.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0507-1482-0954</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 진등로 6 202호</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wo606bc</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>35</v>
+      </c>
+      <c r="R67" t="n">
+        <v>71</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>1718396344</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1718396344</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>PR트레이닝센터</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>prtrainingcenter@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0507-1303-6935</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 경의로 42 영보빌딩 2층</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wkhmdcg</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>26</v>
+      </c>
+      <c r="R68" t="n">
+        <v>38</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>2052414404</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2052414404</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>바디어필 헬스&amp;PT 호원점</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>jguy77@naver.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0507-1388-0985</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 평화로 228 로뎀프라자 4층</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4g4kx</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>433</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>121</v>
+      </c>
+      <c r="R69" t="n">
+        <v>554</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>1963587625</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1963587625</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>짐킹웨이투짐 PT&amp;헬스 산곡점</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>waytogym2gs@naver.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0507-1458-0738</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 서광로 135 센타프라자 203호 웨이투짐</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>113</v>
+      </c>
+      <c r="R70" t="n">
+        <v>170</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>1960822816</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1960822816</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>오운휘트니스&amp;필라테스</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>own0011@naver.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0507-1441-9689</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 녹양로 55 상가동 지하1층</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/oo04.18</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>89</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>127</v>
+      </c>
+      <c r="R71" t="n">
+        <v>216</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>1499021419</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1499021419</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>바디붐휘트니스 의정부역점</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>bodyboom_ujb@naver.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0507-1408-9680</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 태평로99번길 17 베스트프라자 3층</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5vdzl</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>1092</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>609</v>
+      </c>
+      <c r="R72" t="n">
+        <v>1701</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>21598453</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/21598453</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>피트니스플래닛</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>fitnessplanet@naver.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0507-1412-5113</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 신흥로 254 8층</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>http://fitnessplanet.kr/</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wccb3e</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>146</v>
+      </c>
+      <c r="R73" t="n">
+        <v>162</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>493950977</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/493950977</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>골든타임PT 고산점</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>goldentimept@naver.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>0507-1325-8426</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 쌀광길 70 B1층</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>40</v>
+      </c>
+      <c r="R74" t="n">
+        <v>85</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>1725000602</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1725000602</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>부광스포렉스</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>bgspo0088@naver.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0507-1400-0088</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 호국로1351번길 14 부광빌딩</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>378</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>30</v>
+      </c>
+      <c r="R75" t="n">
+        <v>408</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>18549922</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/18549922</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>LT짐 PT</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ph5734@naver.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0507-1397-5346</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 경의로 57 3층</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ph5734</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>117</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>348</v>
+      </c>
+      <c r="R76" t="n">
+        <v>465</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>1470902831</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1470902831</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>비엔드짐 의정부PT</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>bendgym_@naver.com</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>0507-1398-6027</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 시민로 154 해원빌딩 2층 비엔드짐</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4gtg4</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>154</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>256</v>
+      </c>
+      <c r="R77" t="n">
+        <v>410</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>1167910563</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1167910563</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>OPT트레이닝센터 다이어트 피지컬 1:1PT 금오점</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>sunnydue@naver.com</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 청사로 45 플래티넘1프라자 701호</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w45dto</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>4</v>
+      </c>
+      <c r="R78" t="n">
+        <v>12</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>1913501005</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1913501005</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>웨이포 트레이닝센터 PT</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>jerry_training@naver.com</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>0507-1429-1009</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 시민로 27 지층 01,02호 남해오네뜨</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/way_four_pt</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>121</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>204</v>
+      </c>
+      <c r="R79" t="n">
+        <v>325</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>1263561165</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1263561165</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>해머하우스 회룡점 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>hammer_house_2@naver.com</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>0507-1356-0176</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 평화로 389 지하1층</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5yr98</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>366</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>345</v>
+      </c>
+      <c r="R80" t="n">
+        <v>711</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>1470344233</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1470344233</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>피트니스 코바짐</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>jjy41571@naver.com</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>0507-1362-8450</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 금신로 323 7층 701호</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>33</v>
+      </c>
+      <c r="R81" t="n">
+        <v>59</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>1140262254</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1140262254</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>스포애니 의정부역점</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>spoany_62@naver.com</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>0507-1409-9618</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 평화로 540 9, 10 층</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4fckh</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>2032</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>1979</v>
+      </c>
+      <c r="R82" t="n">
+        <v>4011</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>1886274354</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1886274354</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>투제이 휘트니스</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>twojfitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>031-853-7286</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 시민로 405 디유빌딩 2층 투제이휘트니스</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_dxeVTxj</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>141</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>41</v>
+      </c>
+      <c r="R83" t="n">
+        <v>182</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>36414140</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36414140</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>한번더재활운동센터</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>kongja21@naver.com</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 세석로 20 2층 204호</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/weppdix</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>2</v>
+      </c>
+      <c r="R84" t="n">
+        <v>67</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>2072368822</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2072368822</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>아케인짐 헬스PT 줌바 요가 산곡점</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>dlfotjdi2@naver.com</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>0507-1357-0120</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 문충로 116 경기도 의정부시 고산동 989-1</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/b._.young22/</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>177</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>962</v>
+      </c>
+      <c r="R85" t="n">
+        <v>1139</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>1558109890</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1558109890</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>닥터홍짐</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>honghh2029@naver.com</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>0507-1444-0870</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 체육로 306-28 4층 닥터홍짐</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wsevvqt</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>99</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>427</v>
+      </c>
+      <c r="R86" t="n">
+        <v>526</v>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>1318600550</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1318600550</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>새말피트니스 금오점</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>lina9111@naver.com</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>0507-1381-3493</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 금오로 106 2층</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5ufcp</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>252</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>3</v>
+      </c>
+      <c r="R87" t="n">
+        <v>255</v>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>1600728631</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1600728631</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>가능해짐 헬스&amp;PT 1호점</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>9939205@naver.com</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>0507-1379-6449</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 평화로 628 7층</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/9939205</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>84</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>219</v>
+      </c>
+      <c r="R88" t="n">
+        <v>303</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>1491952657</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1491952657</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>여성전용 핏그로우 PT</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>sungkook1027@naver.com</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>0507-1373-5160</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>경기도 의정부시 청사로47번길 18 3층 310호 여성전용 핏그로우PT</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/sungkook1027</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>88</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>263</v>
+      </c>
+      <c r="R89" t="n">
+        <v>351</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>1189641062</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1189641062</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/의정부_PT.xlsx
+++ b/naver-place-crawler/results_health/의정부_PT.xlsx
@@ -596,7 +596,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="Q4" t="n">
         <v>734</v>
       </c>
       <c r="R4" t="n">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -952,29 +952,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>웨이포 트레이닝센터 PT</t>
+          <t>레이디핏 여성전용 PT 헬스</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>jerry_training@naver.com</t>
+          <t>slimfit12@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1429-1009</t>
+          <t>031-847-1318</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 의정부시 시민로 27 지층 01,02호 남해오네뜨</t>
+          <t>경기 의정부시 호국로 1318 우체국 2층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/way_four_pt</t>
+          <t>https://blog.naver.com/slimfit12</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5wzaw</t>
+          <t>https://talk.naver.com/ct/wc32qy</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1013,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>122</v>
+        <v>391</v>
       </c>
       <c r="Q6" t="n">
-        <v>204</v>
+        <v>584</v>
       </c>
       <c r="R6" t="n">
-        <v>326</v>
+        <v>975</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,12 +1028,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1263561165</t>
+          <t>1053007238</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1263561165</t>
+          <t>https://m.place.naver.com/place/1053007238</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1050,29 +1050,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>레이디핏 여성전용 PT 헬스</t>
+          <t>웨이포 트레이닝센터 PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>slimfit12@naver.com</t>
+          <t>jerry_training@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>031-847-1318</t>
+          <t>0507-1429-1009</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 의정부시 호국로 1318 우체국 2층</t>
+          <t>경기 의정부시 시민로 27 지층 01,02호 남해오네뜨</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/slimfit12</t>
+          <t>https://www.instagram.com/way_four_pt</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wc32qy</t>
+          <t>https://talk.naver.com/ct/w5wzaw</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>391</v>
+        <v>122</v>
       </c>
       <c r="Q7" t="n">
-        <v>584</v>
+        <v>204</v>
       </c>
       <c r="R7" t="n">
-        <v>975</v>
+        <v>326</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,12 +1126,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1053007238</t>
+          <t>1263561165</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1053007238</t>
+          <t>https://m.place.naver.com/place/1263561165</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">

--- a/naver-place-crawler/results_health/의정부_PT.xlsx
+++ b/naver-place-crawler/results_health/의정부_PT.xlsx
@@ -426,13 +426,13 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="39" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -596,7 +596,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -679,7 +679,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 의정부시 오목로205번길 21 골든프라자3차 4층 404-1호</t>
+          <t>경기도 의정부시 오목로205번길 21 골든프라자3차 4층 404-1호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -704,14 +704,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4h5hq</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -760,29 +756,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>바디붐휘트니스 민락점 헬스&amp;PT</t>
+          <t>오운휘트니스&amp;필라테스</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>bodyboom_pt@naver.com</t>
+          <t>own0011@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>031-851-3456</t>
+          <t>0507-1441-9689</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 의정부시 오목로225번길 140 성산타워7층</t>
+          <t>경기도 의정부시 녹양로 55 상가동 지하1층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/piece_gym_031_480_6565</t>
+          <t>https://www.instagram.com/oo04.18</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -817,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1170</v>
+        <v>89</v>
       </c>
       <c r="Q4" t="n">
-        <v>734</v>
+        <v>127</v>
       </c>
       <c r="R4" t="n">
-        <v>1904</v>
+        <v>216</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,12 +828,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>36680429</t>
+          <t>1499021419</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36680429</t>
+          <t>https://m.place.naver.com/place/1499021419</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -854,29 +850,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>오운휘트니스&amp;필라테스</t>
+          <t>바디붐휘트니스 민락점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>own0011@naver.com</t>
+          <t>bodyboom_pt@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1441-9689</t>
+          <t>031-851-3456</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 의정부시 녹양로 55 상가동 지하1층</t>
+          <t>경기도 의정부시 오목로225번길 140 성산타워7층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/oo04.18</t>
+          <t>https://www.instagram.com/piece_gym_031_480_6565</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -896,14 +892,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5irz7</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -915,13 +907,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>89</v>
+        <v>1171</v>
       </c>
       <c r="Q5" t="n">
-        <v>127</v>
+        <v>734</v>
       </c>
       <c r="R5" t="n">
-        <v>216</v>
+        <v>1905</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,12 +922,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1499021419</t>
+          <t>36680429</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1499021419</t>
+          <t>https://m.place.naver.com/place/36680429</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -969,7 +961,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 의정부시 호국로 1318 우체국 2층</t>
+          <t>경기도 의정부시 호국로 1318 우체국 2층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -994,14 +986,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc32qy</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1045,34 +1033,34 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>웨이포 트레이닝센터 PT</t>
+          <t>스포애니 의정부역점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>jerry_training@naver.com</t>
+          <t>spoany_62@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1429-1009</t>
+          <t>0507-1409-9618</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 의정부시 시민로 27 지층 01,02호 남해오네뜨</t>
+          <t>경기도 의정부시 평화로 540 9, 10 층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/way_four_pt</t>
+          <t>https://blog.naver.com/spoany_62</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1087,19 +1075,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5wzaw</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1111,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>122</v>
+        <v>2038</v>
       </c>
       <c r="Q7" t="n">
-        <v>204</v>
+        <v>1987</v>
       </c>
       <c r="R7" t="n">
-        <v>326</v>
+        <v>4025</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,12 +1110,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1263561165</t>
+          <t>1886274354</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1263561165</t>
+          <t>https://m.place.naver.com/place/1886274354</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1161,7 +1145,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 의정부시 세석로 20 2층 204호</t>
+          <t>경기도 의정부시 세석로 20 2층 204호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1171,7 +1155,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1186,14 +1170,10 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/weppdix</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1269,7 +1249,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1279,7 +1259,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1331,34 +1311,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>필라테스 림 탑석역 점</t>
+          <t>희핏 PT&amp;헬스</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>pilateslim201@naver.com</t>
+          <t>heegym@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1440-2832</t>
+          <t>0507-1459-0281</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 의정부시 오목로 33 2층 201호</t>
+          <t>경기도 의정부시 평화로 432 지하1층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/pilateslim201/224254625203</t>
+          <t>https://blog.naver.com/heegym</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1378,17 +1358,13 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wjnmgc7</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1397,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>711</v>
+        <v>188</v>
       </c>
       <c r="Q10" t="n">
-        <v>1091</v>
+        <v>455</v>
       </c>
       <c r="R10" t="n">
-        <v>1802</v>
+        <v>643</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1412,12 +1388,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1347002622</t>
+          <t>1135733595</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1347002622</t>
+          <t>https://m.place.naver.com/place/1135733595</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1434,29 +1410,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>희핏 PT&amp;헬스</t>
+          <t>데이짐휘트니스 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>heegym@naver.com</t>
+          <t>daygym_@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1459-0281</t>
+          <t>0507-1410-7247</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 의정부시 평화로 432 지하1층</t>
+          <t>경기도 의정부시 평화로 271-9 상가동 지층 101호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/heegym</t>
+          <t>https://www.instagram.com/daygym_01</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1471,19 +1447,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4e8qf</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1495,13 +1467,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>188</v>
+        <v>107</v>
       </c>
       <c r="Q11" t="n">
-        <v>455</v>
+        <v>86</v>
       </c>
       <c r="R11" t="n">
-        <v>643</v>
+        <v>193</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1510,12 +1482,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1135733595</t>
+          <t>2090105529</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1135733595</t>
+          <t>https://m.place.naver.com/place/2090105529</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/의정부_PT.xlsx
+++ b/naver-place-crawler/results_health/의정부_PT.xlsx
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q6" t="n">
         <v>584</v>
       </c>
       <c r="R6" t="n">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1095,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2038</v>
+        <v>2041</v>
       </c>
       <c r="Q7" t="n">
         <v>1987</v>
       </c>
       <c r="R7" t="n">
-        <v>4025</v>
+        <v>4028</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1316,29 +1316,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>희핏 PT&amp;헬스</t>
+          <t>데이짐휘트니스 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>heegym@naver.com</t>
+          <t>daygym_@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1459-0281</t>
+          <t>0507-1410-7247</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 의정부시 평화로 432 지하1층</t>
+          <t>경기도 의정부시 평화로 271-9 상가동 지층 101호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/heegym</t>
+          <t>https://www.instagram.com/daygym_01</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>188</v>
+        <v>107</v>
       </c>
       <c r="Q10" t="n">
-        <v>455</v>
+        <v>86</v>
       </c>
       <c r="R10" t="n">
-        <v>643</v>
+        <v>193</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1135733595</t>
+          <t>2090105529</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1135733595</t>
+          <t>https://m.place.naver.com/place/2090105529</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1410,29 +1410,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>데이짐휘트니스 헬스&amp;PT</t>
+          <t>바디어필 헬스&amp;PT 호원점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>daygym_@naver.com</t>
+          <t>jguy77@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1410-7247</t>
+          <t>0507-1388-0985</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 의정부시 평화로 271-9 상가동 지층 101호</t>
+          <t>경기도 의정부시 평화로 228 로뎀프라자 4층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/daygym_01</t>
+          <t>https://www.instagram.com/bodyappeal_no.3</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1467,13 +1467,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>107</v>
+        <v>433</v>
       </c>
       <c r="Q11" t="n">
-        <v>86</v>
+        <v>121</v>
       </c>
       <c r="R11" t="n">
-        <v>193</v>
+        <v>554</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,12 +1482,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2090105529</t>
+          <t>1963587625</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2090105529</t>
+          <t>https://m.place.naver.com/place/1963587625</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/의정부_PT.xlsx
+++ b/naver-place-crawler/results_health/의정부_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -432,7 +432,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -1402,6 +1402,104 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>필라테스 림 탑석역 점</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>pilateslim201@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1440-2832</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>경기 의정부시 오목로 33 2층 201호</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/pilateslim201/224254625203</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wjnmgc7</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>711</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1092</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1803</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1347002622</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1347002622</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/naver-place-crawler/results_health/의정부_PT.xlsx
+++ b/naver-place-crawler/results_health/의정부_PT.xlsx
@@ -417,11 +417,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -432,7 +432,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -596,7 +596,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -722,10 +722,10 @@
         <v>358</v>
       </c>
       <c r="Q3" t="n">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="R3" t="n">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -1095,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="Q7" t="n">
-        <v>1987</v>
+        <v>1991</v>
       </c>
       <c r="R7" t="n">
-        <v>4028</v>
+        <v>4033</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1132,29 +1132,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LT짐 PT</t>
+          <t>OPT트레이닝센터 다이어트 피지컬 1:1PT 금오점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ph5734@naver.com</t>
+          <t>sunnydue@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0507-1397-5346</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 의정부시 경의로 57 3층</t>
+          <t>경기도 의정부시 청사로 45 플래티넘1프라자 701호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ph5734</t>
+          <t>https://www.instagram.com/opt087</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1169,7 +1165,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1185,17 +1181,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>117</v>
+        <v>8</v>
       </c>
       <c r="Q8" t="n">
-        <v>348</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>465</v>
+        <v>12</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,12 +1200,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1470902831</t>
+          <t>1913501005</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1470902831</t>
+          <t>https://m.place.naver.com/place/1913501005</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1226,30 +1222,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>한번더재활운동센터</t>
+          <t>LT짐 PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>kongja21@naver.com</t>
+          <t>ph5734@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0507-1397-5346</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 의정부시 세석로 20 2층 204호</t>
+          <t>경기도 의정부시 경의로 57 3층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://youtube.com/@한번더재활운동센터</t>
+          <t>https://blog.naver.com/ph5734</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>348</v>
       </c>
       <c r="R9" t="n">
-        <v>67</v>
+        <v>465</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2072368822</t>
+          <t>1470902831</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2072368822</t>
+          <t>https://m.place.naver.com/place/1470902831</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1311,34 +1311,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>코스트짐PT 민락점</t>
+          <t>아테나휘트니스</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>costgymjun@naver.com</t>
+          <t>athenagym@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>031-853-1663</t>
+          <t>0507-1334-7642</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 의정부시 오목로205번길 21 골든프라자 3차 202호</t>
+          <t>경기도 의정부시 시민로121번길 28 지하1층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/costgym</t>
+          <t>https://blog.naver.com/athenagym</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>90</v>
+        <v>2916</v>
       </c>
       <c r="Q10" t="n">
-        <v>84</v>
+        <v>968</v>
       </c>
       <c r="R10" t="n">
-        <v>174</v>
+        <v>3884</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>38447811</t>
+          <t>1788806049</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38447811</t>
+          <t>https://m.place.naver.com/place/1788806049</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1405,34 +1405,30 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>필라테스 림 탑석역 점</t>
+          <t>한번더재활운동센터</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>pilateslim201@naver.com</t>
+          <t>kongja21@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1440-2832</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 의정부시 오목로 33 2층 201호</t>
+          <t>경기도 의정부시 세석로 20 2층 204호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/pilateslim201/224254625203</t>
+          <t>https://youtube.com/@한번더재활운동센터</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1447,37 +1443,33 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wjnmgc7</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>711</v>
+        <v>65</v>
       </c>
       <c r="Q11" t="n">
-        <v>1092</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>1803</v>
+        <v>67</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1486,15 +1478,109 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1347002622</t>
+          <t>2072368822</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1347002622</t>
+          <t>https://m.place.naver.com/place/2072368822</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>코스트짐PT 민락점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>costgymjun@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>031-853-1663</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>경기 의정부시 오목로205번길 21 골든프라자 3차 202호</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/costgym</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>84</v>
+      </c>
+      <c r="R12" t="n">
+        <v>174</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>38447811</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38447811</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_health/의정부_PT.xlsx
+++ b/naver-place-crawler/results_health/의정부_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,13 +426,13 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="39" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 의정부시 오목로205번길 21 골든프라자3차 4층 404-1호</t>
+          <t>경기 의정부시 오목로205번길 21 골든프라자3차 4층 404-1호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -704,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4h5hq</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -744,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -773,7 +777,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 의정부시 녹양로 55 상가동 지하1층</t>
+          <t>경기 의정부시 녹양로 55 상가동 지하1층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -798,10 +802,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5irz7</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -838,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -867,7 +875,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 의정부시 오목로225번길 140 성산타워7층</t>
+          <t>경기 의정부시 오목로225번길 140 성산타워7층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -932,7 +940,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -961,7 +969,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 의정부시 호국로 1318 우체국 2층</t>
+          <t>경기 의정부시 호국로 1318 우체국 2층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -986,10 +994,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc32qy</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1026,7 +1038,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1055,7 +1067,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 의정부시 평화로 540 9, 10 층</t>
+          <t>경기 의정부시 평화로 540 9, 10 층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1080,10 +1092,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4fckh</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1120,7 +1136,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1161,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 의정부시 청사로 45 플래티넘1프라자 701호</t>
+          <t>경기 의정부시 청사로 45 플래티넘1프라자 701호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1170,10 +1186,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w45dto</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1210,7 +1230,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1222,29 +1242,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LT짐 PT</t>
+          <t>한번더재활운동센터</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ph5734@naver.com</t>
+          <t>kongja21@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0507-1397-5346</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 의정부시 경의로 57 3층</t>
+          <t>경기 의정부시 세석로 20 2층 204호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ph5734</t>
+          <t>https://youtube.com/@한번더재활운동센터</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1259,15 +1275,19 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/weppdix</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1279,13 +1299,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>117</v>
+        <v>65</v>
       </c>
       <c r="Q9" t="n">
-        <v>348</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>465</v>
+        <v>67</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,51 +1314,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1470902831</t>
+          <t>2072368822</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1470902831</t>
+          <t>https://m.place.naver.com/place/2072368822</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>아테나휘트니스</t>
+          <t>코스트짐PT 민락점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>athenagym@naver.com</t>
+          <t>costgymjun@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1334-7642</t>
+          <t>031-853-1663</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 의정부시 시민로121번길 28 지하1층</t>
+          <t>경기 의정부시 오목로205번길 21 골든프라자 3차 202호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/athenagym</t>
+          <t>https://www.instagram.com/costgym</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1353,7 +1373,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1373,13 +1393,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2916</v>
+        <v>90</v>
       </c>
       <c r="Q10" t="n">
-        <v>968</v>
+        <v>84</v>
       </c>
       <c r="R10" t="n">
-        <v>3884</v>
+        <v>174</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,47 +1408,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1788806049</t>
+          <t>38447811</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1788806049</t>
+          <t>https://m.place.naver.com/place/38447811</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>한번더재활운동센터</t>
+          <t>희핏 PT&amp;헬스</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>kongja21@naver.com</t>
+          <t>heegym@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1459-0281</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 의정부시 세석로 20 2층 204호</t>
+          <t>경기 의정부시 평화로 432 지하1층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://youtube.com/@한번더재활운동센터</t>
+          <t>https://blog.naver.com/heegym</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1443,15 +1467,19 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4e8qf</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1459,17 +1487,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>65</v>
+        <v>188</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>456</v>
       </c>
       <c r="R11" t="n">
-        <v>67</v>
+        <v>644</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1478,111 +1506,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2072368822</t>
+          <t>1135733595</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2072368822</t>
+          <t>https://m.place.naver.com/place/1135733595</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>코스트짐PT 민락점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>costgymjun@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>031-853-1663</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>경기 의정부시 오목로205번길 21 골든프라자 3차 202호</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/costgym</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>90</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>84</v>
-      </c>
-      <c r="R12" t="n">
-        <v>174</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>38447811</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/38447811</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/의정부_PT.xlsx
+++ b/naver-place-crawler/results_health/의정부_PT.xlsx
@@ -628,10 +628,10 @@
         <v>668</v>
       </c>
       <c r="Q2" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="R2" t="n">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -726,10 +726,10 @@
         <v>358</v>
       </c>
       <c r="Q3" t="n">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="R3" t="n">
-        <v>1855</v>
+        <v>1856</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1016,10 +1016,10 @@
         <v>392</v>
       </c>
       <c r="Q6" t="n">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="R6" t="n">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1114,10 +1114,10 @@
         <v>2042</v>
       </c>
       <c r="Q7" t="n">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="R7" t="n">
-        <v>4033</v>
+        <v>4032</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1242,25 +1242,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>한번더재활운동센터</t>
+          <t>LT짐 PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>kongja21@naver.com</t>
+          <t>ph5734@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0507-1397-5346</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 의정부시 세석로 20 2층 204호</t>
+          <t>경기 의정부시 경의로 57 3층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://youtube.com/@한번더재활운동센터</t>
+          <t>https://blog.naver.com/ph5734</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1275,7 +1279,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1285,7 +1289,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/weppdix</t>
+          <t>https://talk.naver.com/ct/w5wjfa</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1299,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>348</v>
       </c>
       <c r="R9" t="n">
-        <v>67</v>
+        <v>465</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1314,12 +1318,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2072368822</t>
+          <t>1470902831</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2072368822</t>
+          <t>https://m.place.naver.com/place/1470902831</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1336,29 +1340,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>코스트짐PT 민락점</t>
+          <t>한번더재활운동센터</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>costgymjun@naver.com</t>
+          <t>kongja21@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>031-853-1663</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 의정부시 오목로205번길 21 골든프라자 3차 202호</t>
+          <t>경기 의정부시 세석로 20 2층 204호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/costgym</t>
+          <t>https://youtube.com/@한번더재활운동센터</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1378,10 +1378,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/weppdix</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1389,17 +1393,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="Q10" t="n">
-        <v>84</v>
+        <v>2</v>
       </c>
       <c r="R10" t="n">
-        <v>174</v>
+        <v>67</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1408,12 +1412,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>38447811</t>
+          <t>2072368822</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38447811</t>
+          <t>https://m.place.naver.com/place/2072368822</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1425,34 +1429,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>희핏 PT&amp;헬스</t>
+          <t>코스트짐PT 민락점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>heegym@naver.com</t>
+          <t>costgymjun@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1459-0281</t>
+          <t>031-853-1663</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 의정부시 평화로 432 지하1층</t>
+          <t>경기 의정부시 오목로205번길 21 골든프라자 3차 202호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/heegym</t>
+          <t>https://www.instagram.com/costgym</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1467,19 +1471,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4e8qf</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1491,13 +1491,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>188</v>
+        <v>90</v>
       </c>
       <c r="Q11" t="n">
-        <v>456</v>
+        <v>84</v>
       </c>
       <c r="R11" t="n">
-        <v>644</v>
+        <v>174</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1506,12 +1506,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1135733595</t>
+          <t>38447811</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1135733595</t>
+          <t>https://m.place.naver.com/place/38447811</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/의정부_PT.xlsx
+++ b/naver-place-crawler/results_health/의정부_PT.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1114,10 +1114,10 @@
         <v>2042</v>
       </c>
       <c r="Q7" t="n">
-        <v>1990</v>
+        <v>1987</v>
       </c>
       <c r="R7" t="n">
-        <v>4032</v>
+        <v>4029</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1242,29 +1242,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LT짐 PT</t>
+          <t>한번더재활운동센터</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ph5734@naver.com</t>
+          <t>kongja21@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0507-1397-5346</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 의정부시 경의로 57 3층</t>
+          <t>경기 의정부시 세석로 20 2층 204호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ph5734</t>
+          <t>https://youtube.com/@한번더재활운동센터</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1279,7 +1275,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1289,7 +1285,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5wjfa</t>
+          <t>https://talk.naver.com/ct/weppdix</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1303,13 +1299,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>117</v>
+        <v>65</v>
       </c>
       <c r="Q9" t="n">
-        <v>348</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>465</v>
+        <v>67</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,17 +1314,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1470902831</t>
+          <t>2072368822</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1470902831</t>
+          <t>https://m.place.naver.com/place/2072368822</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1340,25 +1336,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>한번더재활운동센터</t>
+          <t>코스트짐PT 민락점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>kongja21@naver.com</t>
+          <t>costgymjun@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>031-853-1663</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 의정부시 세석로 20 2층 204호</t>
+          <t>경기 의정부시 오목로205번길 21 골든프라자 3차 202호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://youtube.com/@한번더재활운동센터</t>
+          <t>https://www.instagram.com/costgym</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1378,14 +1378,10 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/weppdix</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1393,17 +1389,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>84</v>
       </c>
       <c r="R10" t="n">
-        <v>67</v>
+        <v>174</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1412,51 +1408,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2072368822</t>
+          <t>38447811</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2072368822</t>
+          <t>https://m.place.naver.com/place/38447811</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>코스트짐PT 민락점</t>
+          <t>필라테스 림 탑석역 점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>costgymjun@naver.com</t>
+          <t>pilateslim201@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>031-853-1663</t>
+          <t>0507-1440-2832</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 의정부시 오목로205번길 21 골든프라자 3차 202호</t>
+          <t>경기 의정부시 오목로 33 2층 201호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/costgym</t>
+          <t>https://blog.naver.com/pilateslim201/224254625203</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1471,18 +1467,22 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wjnmgc7</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1491,13 +1491,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>90</v>
+        <v>712</v>
       </c>
       <c r="Q11" t="n">
-        <v>84</v>
+        <v>1093</v>
       </c>
       <c r="R11" t="n">
-        <v>174</v>
+        <v>1805</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1506,17 +1506,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>38447811</t>
+          <t>1347002622</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38447811</t>
+          <t>https://m.place.naver.com/place/1347002622</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/의정부_PT.xlsx
+++ b/naver-place-crawler/results_health/의정부_PT.xlsx
@@ -421,13 +421,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="39" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -569,7 +569,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>madeline-@naver.com</t>
+          <t>made-line@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -667,7 +667,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>hue_musculoskeleta@naver.com</t>
+          <t>bumt900@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -684,7 +684,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hue_musculoskeleta</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,12 +694,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/oo04.18</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/piece_gym_031_480_6565</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/slimfit12</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -984,12 +984,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spoany_62</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1082,12 +1082,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OPT트레이닝센터 다이어트 피지컬 1:1PT 금오점</t>
+          <t>한번더재활운동센터</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>sunnydue@naver.com</t>
+          <t>kongja21@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -1161,12 +1161,12 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 의정부시 청사로 45 플래티넘1프라자 701호</t>
+          <t>경기 의정부시 세석로 20 2층 204호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/opt087</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w45dto</t>
+          <t>https://talk.naver.com/ct/weppdix</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1201,17 +1201,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1913501005</t>
+          <t>2072368822</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1913501005</t>
+          <t>https://m.place.naver.com/place/2072368822</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1242,25 +1242,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>한번더재활운동센터</t>
+          <t>코스트짐PT 민락점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>kongja21@naver.com</t>
+          <t>costgymjun@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>031-853-1663</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 의정부시 세석로 20 2층 204호</t>
+          <t>경기 의정부시 오목로205번길 21 골든프라자 3차 202호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://youtube.com/@한번더재활운동센터</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1270,7 +1274,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1280,14 +1284,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/weppdix</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1295,17 +1295,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>84</v>
       </c>
       <c r="R9" t="n">
-        <v>67</v>
+        <v>174</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1314,12 +1314,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2072368822</t>
+          <t>38447811</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2072368822</t>
+          <t>https://m.place.naver.com/place/38447811</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1331,34 +1331,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>코스트짐PT 민락점</t>
+          <t>필라테스 림 탑석역 점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>costgymjun@naver.com</t>
+          <t>pilateslim201@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>031-853-1663</t>
+          <t>0507-1440-2832</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 의정부시 오목로205번길 21 골든프라자 3차 202호</t>
+          <t>경기 의정부시 오목로 33 2층 201호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/costgym</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1378,13 +1378,17 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wjnmgc7</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1393,13 +1397,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>90</v>
+        <v>712</v>
       </c>
       <c r="Q10" t="n">
-        <v>84</v>
+        <v>1093</v>
       </c>
       <c r="R10" t="n">
-        <v>174</v>
+        <v>1805</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1408,12 +1412,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>38447811</t>
+          <t>1347002622</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38447811</t>
+          <t>https://m.place.naver.com/place/1347002622</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1425,34 +1429,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>필라테스 림 탑석역 점</t>
+          <t>희핏 PT&amp;헬스</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>pilateslim201@naver.com</t>
+          <t>heegym@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1440-2832</t>
+          <t>0507-1459-0281</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 의정부시 오목로 33 2층 201호</t>
+          <t>경기 의정부시 평화로 432 지하1층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/pilateslim201/224254625203</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1462,12 +1466,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1477,12 +1481,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wjnmgc7</t>
+          <t>https://talk.naver.com/ct/w4e8qf</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1491,13 +1495,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>712</v>
+        <v>188</v>
       </c>
       <c r="Q11" t="n">
-        <v>1093</v>
+        <v>456</v>
       </c>
       <c r="R11" t="n">
-        <v>1805</v>
+        <v>644</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1506,12 +1510,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1347002622</t>
+          <t>1135733595</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1347002622</t>
+          <t>https://m.place.naver.com/place/1135733595</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
